--- a/Bao cao/MWG/MWG_Model_2026_07_05.xlsx
+++ b/Bao cao/MWG/MWG_Model_2026_07_05.xlsx
@@ -41397,7 +41397,7 @@
       </c>
       <c r="B17" s="13" t="inlineStr">
         <is>
-          <t>05/07/2026 03:19</t>
+          <t>05/07/2026 03:28</t>
         </is>
       </c>
     </row>
@@ -43351,7 +43351,9 @@
       <c r="AJ3" s="32" t="n">
         <v>0.2688</v>
       </c>
-      <c r="AK3" s="32" t="n"/>
+      <c r="AK3" s="32" t="n">
+        <v>0.2688</v>
+      </c>
       <c r="AL3" s="32" t="n">
         <v>0.2689</v>
       </c>
@@ -43558,10 +43560,10 @@
         <v>0.631</v>
       </c>
       <c r="O4" s="32" t="n">
-        <v>0.4691</v>
+        <v>0.631</v>
       </c>
       <c r="P4" s="32" t="n">
-        <v>0.5072</v>
+        <v>0.631</v>
       </c>
       <c r="Q4" s="32" t="n">
         <v>0.5545</v>
@@ -43609,10 +43611,10 @@
         <v>0.5281</v>
       </c>
       <c r="AF4" s="32" t="n">
-        <v>0.389</v>
+        <v>0.5281</v>
       </c>
       <c r="AG4" s="32" t="n">
-        <v>0.3572</v>
+        <v>0.5281</v>
       </c>
       <c r="AH4" s="32" t="n">
         <v>0.4906</v>
@@ -43623,7 +43625,9 @@
       <c r="AJ4" s="32" t="n">
         <v>0.5665</v>
       </c>
-      <c r="AK4" s="32" t="n"/>
+      <c r="AK4" s="32" t="n">
+        <v>0.5665</v>
+      </c>
       <c r="AL4" s="32" t="n">
         <v>0.5703</v>
       </c>
@@ -43881,10 +43885,10 @@
         <v>0.2578</v>
       </c>
       <c r="AF5" s="32" t="n">
-        <v>0.4413</v>
+        <v>0.2578</v>
       </c>
       <c r="AG5" s="32" t="n">
-        <v>0.4731</v>
+        <v>0.2578</v>
       </c>
       <c r="AH5" s="32" t="n">
         <v>0.2317</v>
@@ -43895,7 +43899,9 @@
       <c r="AJ5" s="32" t="n">
         <v>0.1521</v>
       </c>
-      <c r="AK5" s="32" t="n"/>
+      <c r="AK5" s="32" t="n">
+        <v>0.149</v>
+      </c>
       <c r="AL5" s="32" t="n">
         <v>0.1536</v>
       </c>
@@ -44369,7 +44375,10 @@
         <f>AJ$2*AJ$3</f>
         <v/>
       </c>
-      <c r="AK8" s="33" t="n"/>
+      <c r="AK8" s="33">
+        <f>AK$2*AK$3</f>
+        <v/>
+      </c>
       <c r="AL8" s="33">
         <f>AL$2*AL$3</f>
         <v/>
@@ -44741,7 +44750,10 @@
         <f>AJ$2*AJ$4</f>
         <v/>
       </c>
-      <c r="AK9" s="33" t="n"/>
+      <c r="AK9" s="33">
+        <f>AK$2*AK$4</f>
+        <v/>
+      </c>
       <c r="AL9" s="33">
         <f>AL$2*AL$4</f>
         <v/>
@@ -45113,7 +45125,10 @@
         <f>AJ$2*AJ$5</f>
         <v/>
       </c>
-      <c r="AK10" s="33" t="n"/>
+      <c r="AK10" s="33">
+        <f>AK$2*AK$5</f>
+        <v/>
+      </c>
       <c r="AL10" s="33">
         <f>AL$2*AL$5</f>
         <v/>

--- a/Bao cao/MWG/MWG_Model_2026_07_05.xlsx
+++ b/Bao cao/MWG/MWG_Model_2026_07_05.xlsx
@@ -41397,7 +41397,7 @@
       </c>
       <c r="B17" s="13" t="inlineStr">
         <is>
-          <t>05/07/2026 03:28</t>
+          <t>05/07/2026 10:50</t>
         </is>
       </c>
     </row>
